--- a/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-15).xlsx
+++ b/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-15).xlsx
@@ -912,21 +912,21 @@
   </si>
   <si>
     <t>214
-171</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>R$ 966.841,85</t>
-  </si>
-  <si>
-    <t>R$ 5.312,32
-R$ 5.453,35</t>
-  </si>
-  <si>
-    <t>(0.8%)
-1.8%</t>
+172</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>R$ 971.628,98</t>
+  </si>
+  <si>
+    <t>R$ 5.309,45
+R$ 5.449,48</t>
+  </si>
+  <si>
+    <t>(0.9%)
+1.7%</t>
   </si>
   <si>
     <t>55.4</t>
@@ -935,7 +935,7 @@
     <t>(5.1%)</t>
   </si>
   <si>
-    <t>37.0%</t>
+    <t>36.9%</t>
   </si>
   <si>
     <t>(10.3%)</t>
@@ -959,7 +959,7 @@
     <t>5.6</t>
   </si>
   <si>
-    <t>6.8</t>
+    <t>6.9</t>
   </si>
   <si>
     <t>12.5</t>
@@ -968,13 +968,13 @@
     <t>19.1</t>
   </si>
   <si>
-    <t>69.8%</t>
+    <t>69.7%</t>
   </si>
   <si>
     <t>-R$ 31.492,95</t>
   </si>
   <si>
-    <t>2.97</t>
+    <t>2.95</t>
   </si>
   <si>
     <t>3.52</t>
@@ -6674,7 +6674,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>44</v>
@@ -6710,25 +6710,59 @@
       <c t="s" r="N42" s="4">
         <v>52</v>
       </c>
-      <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="6"/>
-      <c r="R42" s="7"/>
-      <c r="S42" s="6"/>
-      <c r="T42" s="6"/>
-      <c r="U42" s="6"/>
-      <c r="V42" s="6"/>
-      <c r="W42" s="6"/>
-      <c r="X42" s="8"/>
-      <c r="Y42" s="6"/>
-      <c r="Z42" s="6"/>
-      <c r="AA42" s="8"/>
-      <c r="AB42" s="8"/>
+      <c r="O42" s="5">
+        <v>4787.1300000000001</v>
+      </c>
+      <c r="P42" s="5">
+        <v>4787.1300000000001</v>
+      </c>
+      <c r="Q42" s="6">
+        <v>-0.16975290977486635</v>
+      </c>
+      <c r="R42" s="7">
+        <v>49</v>
+      </c>
+      <c r="S42" s="6">
+        <v>-0.10909090909090913</v>
+      </c>
+      <c r="T42" s="6">
+        <v>0.34327135465299669</v>
+      </c>
+      <c r="U42" s="6">
+        <v>0.024773632635838174</v>
+      </c>
+      <c r="V42" s="6">
+        <v>0.040803675688773862</v>
+      </c>
+      <c r="W42" s="6">
+        <v>-0.0042045024889652048</v>
+      </c>
+      <c r="X42" s="8">
+        <v>31.168055555555554</v>
+      </c>
+      <c r="Y42" s="6">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="Z42" s="6">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="AA42" s="8">
+        <v>7.0221081632653064</v>
+      </c>
+      <c r="AB42" s="8">
+        <v>11.97258064516129</v>
+      </c>
       <c r="AC42" s="8"/>
-      <c r="AD42" s="8"/>
-      <c r="AE42" s="6"/>
+      <c r="AD42" s="8">
+        <v>25.049075000000002</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>0.63888888888888884</v>
+      </c>
       <c r="AF42" s="9"/>
-      <c r="AG42" s="5"/>
+      <c r="AG42" s="5">
+        <v>0</v>
+      </c>
       <c r="AH42" s="10">
         <v>3</v>
       </c>
@@ -15297,7 +15331,7 @@
         <v>0</v>
       </c>
       <c r="AH111" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI111" s="11"/>
       <c r="AJ111" s="13">
@@ -15650,7 +15684,7 @@
         <v>-219.19999999999999</v>
       </c>
       <c r="AH114" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI114" s="11"/>
       <c r="AJ114" s="13">

--- a/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-15).xlsx
+++ b/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-15).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-172</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>R$ 971.628,98</t>
-  </si>
-  <si>
-    <t>R$ 5.309,45
-R$ 5.449,48</t>
-  </si>
-  <si>
-    <t>(0.9%)
-1.7%</t>
-  </si>
-  <si>
-    <t>55.4</t>
-  </si>
-  <si>
-    <t>(5.1%)</t>
+173</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>R$ 973.448,43</t>
+  </si>
+  <si>
+    <t>R$ 5.290,48
+R$ 5.428,49</t>
+  </si>
+  <si>
+    <t>(1.1%)
+1.5%</t>
+  </si>
+  <si>
+    <t>55.2</t>
+  </si>
+  <si>
+    <t>(5.3%)</t>
   </si>
   <si>
     <t>36.9%</t>
   </si>
   <si>
-    <t>(10.3%)</t>
+    <t>(10.2%)</t>
   </si>
   <si>
     <t>3.5%</t>
@@ -950,7 +950,7 @@
     <t>27.3</t>
   </si>
   <si>
-    <t>70.0%</t>
+    <t>69.8%</t>
   </si>
   <si>
     <t>10.4%</t>
@@ -974,7 +974,7 @@
     <t>-R$ 31.492,95</t>
   </si>
   <si>
-    <t>2.95</t>
+    <t>2.94</t>
   </si>
   <si>
     <t>3.52</t>
@@ -6752,7 +6752,9 @@
       <c r="AB42" s="8">
         <v>11.97258064516129</v>
       </c>
-      <c r="AC42" s="8"/>
+      <c r="AC42" s="8">
+        <v>20.112393999999998</v>
+      </c>
       <c r="AD42" s="8">
         <v>25.049075000000002</v>
       </c>
@@ -14178,7 +14180,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>44</v>
@@ -14214,25 +14216,57 @@
       <c t="s" r="N102" s="4">
         <v>52</v>
       </c>
-      <c r="O102" s="5"/>
-      <c r="P102" s="5"/>
-      <c r="Q102" s="6"/>
-      <c r="R102" s="7"/>
-      <c r="S102" s="6"/>
-      <c r="T102" s="6"/>
-      <c r="U102" s="6"/>
-      <c r="V102" s="6"/>
-      <c r="W102" s="6"/>
-      <c r="X102" s="8"/>
-      <c r="Y102" s="6"/>
-      <c r="Z102" s="6"/>
-      <c r="AA102" s="8"/>
+      <c r="O102" s="5">
+        <v>1819.45</v>
+      </c>
+      <c r="P102" s="5">
+        <v>1819.45</v>
+      </c>
+      <c r="Q102" s="6">
+        <v>-0.43329907182458105</v>
+      </c>
+      <c r="R102" s="7">
+        <v>19</v>
+      </c>
+      <c r="S102" s="6">
+        <v>-0.52500000000000002</v>
+      </c>
+      <c r="T102" s="6">
+        <v>0.35370996729780974</v>
+      </c>
+      <c r="U102" s="6">
+        <v>-0.010334111956910055</v>
+      </c>
+      <c r="V102" s="6">
+        <v>0.11142927807854022</v>
+      </c>
+      <c r="W102" s="6">
+        <v>0.068570172304817392</v>
+      </c>
+      <c r="X102" s="8">
+        <v>5.9166999999999996</v>
+      </c>
+      <c r="Y102" s="6">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="Z102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="8">
+        <v>4.1341650000000003</v>
+      </c>
       <c r="AB102" s="8"/>
       <c r="AC102" s="8"/>
-      <c r="AD102" s="8"/>
-      <c r="AE102" s="6"/>
+      <c r="AD102" s="8">
+        <v>0.29999999999999999</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>1</v>
+      </c>
       <c r="AF102" s="9"/>
-      <c r="AG102" s="5"/>
+      <c r="AG102" s="5">
+        <v>0</v>
+      </c>
       <c r="AH102" s="10">
         <v>2</v>
       </c>
@@ -15319,7 +15353,9 @@
       <c r="AB111" s="8">
         <v>0.97778333333333334</v>
       </c>
-      <c r="AC111" s="8"/>
+      <c r="AC111" s="8">
+        <v>6.272221</v>
+      </c>
       <c r="AD111" s="8">
         <v>13.216666666666667</v>
       </c>
@@ -17214,7 +17250,7 @@
         <v>0</v>
       </c>
       <c r="AH126" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI126" s="11"/>
       <c r="AJ126" s="13">
@@ -18377,7 +18413,7 @@
         <v>0</v>
       </c>
       <c r="AH135" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI135" s="11"/>
       <c r="AJ135" s="13">
@@ -20695,7 +20731,7 @@
         <v>-2211.52</v>
       </c>
       <c r="AH153" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI153" s="11"/>
       <c r="AJ153" s="13">
@@ -21907,7 +21943,7 @@
         <v>-2149.9299999999998</v>
       </c>
       <c r="AH163" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI163" s="11"/>
       <c r="AJ163" s="13">
@@ -27980,7 +28016,7 @@
       <c r="AF212" s="9"/>
       <c r="AG212" s="5"/>
       <c r="AH212" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI212" s="11"/>
       <c r="AJ212" s="12"/>

--- a/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-15).xlsx
+++ b/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-15).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-173</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>R$ 973.448,43</t>
-  </si>
-  <si>
-    <t>R$ 5.290,48
-R$ 5.428,49</t>
-  </si>
-  <si>
-    <t>(1.1%)
-1.5%</t>
-  </si>
-  <si>
-    <t>55.2</t>
-  </si>
-  <si>
-    <t>(5.3%)</t>
-  </si>
-  <si>
-    <t>36.9%</t>
-  </si>
-  <si>
-    <t>(10.2%)</t>
+175</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R$ 983.571,78</t>
+  </si>
+  <si>
+    <t>R$ 5.288,02
+R$ 5.424,30</t>
+  </si>
+  <si>
+    <t>(1.4%)
+1.1%</t>
+  </si>
+  <si>
+    <t>55.3</t>
+  </si>
+  <si>
+    <t>(5.5%)</t>
+  </si>
+  <si>
+    <t>37.4%</t>
+  </si>
+  <si>
+    <t>(9.8%)</t>
   </si>
   <si>
     <t>3.5%</t>
@@ -950,16 +950,16 @@
     <t>27.3</t>
   </si>
   <si>
-    <t>69.8%</t>
-  </si>
-  <si>
-    <t>10.4%</t>
+    <t>69.6%</t>
+  </si>
+  <si>
+    <t>10.3%</t>
   </si>
   <si>
     <t>5.6</t>
   </si>
   <si>
-    <t>6.9</t>
+    <t>6.8</t>
   </si>
   <si>
     <t>12.5</t>
@@ -971,10 +971,10 @@
     <t>69.7%</t>
   </si>
   <si>
-    <t>-R$ 31.492,95</t>
-  </si>
-  <si>
-    <t>2.94</t>
+    <t>-R$ 31.922,75</t>
+  </si>
+  <si>
+    <t>2.95</t>
   </si>
   <si>
     <t>3.52</t>
@@ -10938,7 +10938,7 @@
         <v>19661</v>
       </c>
       <c r="B76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C76" s="4">
         <v>44</v>
@@ -10972,25 +10972,61 @@
       <c t="s" r="N76" s="4">
         <v>52</v>
       </c>
-      <c r="O76" s="5"/>
-      <c r="P76" s="5"/>
-      <c r="Q76" s="6"/>
-      <c r="R76" s="7"/>
-      <c r="S76" s="6"/>
-      <c r="T76" s="6"/>
-      <c r="U76" s="6"/>
-      <c r="V76" s="6"/>
-      <c r="W76" s="6"/>
-      <c r="X76" s="8"/>
-      <c r="Y76" s="6"/>
-      <c r="Z76" s="6"/>
-      <c r="AA76" s="8"/>
-      <c r="AB76" s="8"/>
-      <c r="AC76" s="8"/>
-      <c r="AD76" s="8"/>
-      <c r="AE76" s="6"/>
+      <c r="O76" s="5">
+        <v>5519.0799999999999</v>
+      </c>
+      <c r="P76" s="5">
+        <v>5519.0799999999999</v>
+      </c>
+      <c r="Q76" s="6">
+        <v>-0.42032559605083497</v>
+      </c>
+      <c r="R76" s="7">
+        <v>69</v>
+      </c>
+      <c r="S76" s="6">
+        <v>-0.35514018691588789</v>
+      </c>
+      <c r="T76" s="6">
+        <v>1.0914365981286738</v>
+      </c>
+      <c r="U76" s="6">
+        <v>0.67986800336287934</v>
+      </c>
+      <c r="V76" s="6">
+        <v>0.02096218935039898</v>
+      </c>
+      <c r="W76" s="6">
+        <v>-0.014503866586460063</v>
+      </c>
+      <c r="X76" s="8">
+        <v>29.789655172413791</v>
+      </c>
+      <c r="Y76" s="6">
+        <v>0.48275862068965519</v>
+      </c>
+      <c r="Z76" s="6">
+        <v>0.10344827586206896</v>
+      </c>
+      <c r="AA76" s="8">
+        <v>5.7915492957746482</v>
+      </c>
+      <c r="AB76" s="8">
+        <v>5.9434782608695649</v>
+      </c>
+      <c r="AC76" s="8">
+        <v>12.138636</v>
+      </c>
+      <c r="AD76" s="8">
+        <v>19</v>
+      </c>
+      <c r="AE76" s="6">
+        <v>0.55172413793103448</v>
+      </c>
       <c r="AF76" s="9"/>
-      <c r="AG76" s="5"/>
+      <c r="AG76" s="5">
+        <v>-227.44999999999999</v>
+      </c>
       <c r="AH76" s="10">
         <v>2</v>
       </c>
@@ -16857,7 +16893,7 @@
         <v>0</v>
       </c>
       <c r="AH123" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI123" s="11"/>
       <c r="AJ123" s="13">
@@ -25943,7 +25979,7 @@
         <v>19944</v>
       </c>
       <c r="B195" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C195" s="4">
         <v>44</v>
@@ -25979,25 +26015,59 @@
       <c t="s" r="N195" s="4">
         <v>52</v>
       </c>
-      <c r="O195" s="5"/>
-      <c r="P195" s="5"/>
-      <c r="Q195" s="6"/>
-      <c r="R195" s="7"/>
-      <c r="S195" s="6"/>
-      <c r="T195" s="6"/>
-      <c r="U195" s="6"/>
-      <c r="V195" s="6"/>
-      <c r="W195" s="6"/>
-      <c r="X195" s="8"/>
-      <c r="Y195" s="6"/>
-      <c r="Z195" s="6"/>
-      <c r="AA195" s="8"/>
-      <c r="AB195" s="8"/>
+      <c r="O195" s="5">
+        <v>4604.2700000000004</v>
+      </c>
+      <c r="P195" s="5">
+        <v>4604.2700000000004</v>
+      </c>
+      <c r="Q195" s="6">
+        <v>0.17280843638957188</v>
+      </c>
+      <c r="R195" s="7">
+        <v>56</v>
+      </c>
+      <c r="S195" s="6">
+        <v>0.12000000000000011</v>
+      </c>
+      <c r="T195" s="6">
+        <v>0.38114624033777339</v>
+      </c>
+      <c r="U195" s="6">
+        <v>0.015754983960540973</v>
+      </c>
+      <c r="V195" s="6">
+        <v>0.016280105206688572</v>
+      </c>
+      <c r="W195" s="6">
+        <v>-0.0090919950393873513</v>
+      </c>
+      <c r="X195" s="8">
+        <v>26.860937499999999</v>
+      </c>
+      <c r="Y195" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Z195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA195" s="8">
+        <v>6.949320408163266</v>
+      </c>
+      <c r="AB195" s="8">
+        <v>5.5406250000000004</v>
+      </c>
       <c r="AC195" s="8"/>
-      <c r="AD195" s="8"/>
-      <c r="AE195" s="6"/>
+      <c r="AD195" s="8">
+        <v>19.720834374999999</v>
+      </c>
+      <c r="AE195" s="6">
+        <v>0.71875</v>
+      </c>
       <c r="AF195" s="9"/>
-      <c r="AG195" s="5"/>
+      <c r="AG195" s="5">
+        <v>-202.34999999999999</v>
+      </c>
       <c r="AH195" s="10">
         <v>2</v>
       </c>

--- a/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-15).xlsx
+++ b/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-15).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-175</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>R$ 983.571,78</t>
-  </si>
-  <si>
-    <t>R$ 5.288,02
-R$ 5.424,30</t>
-  </si>
-  <si>
-    <t>(1.4%)
-1.1%</t>
-  </si>
-  <si>
-    <t>55.3</t>
-  </si>
-  <si>
-    <t>(5.5%)</t>
+176</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>R$ 990.386,63</t>
+  </si>
+  <si>
+    <t>R$ 5.296,19
+R$ 5.432,20</t>
+  </si>
+  <si>
+    <t>(1.3%)
+1.3%</t>
+  </si>
+  <si>
+    <t>55.4</t>
+  </si>
+  <si>
+    <t>(5.4%)</t>
   </si>
   <si>
     <t>37.4%</t>
   </si>
   <si>
-    <t>(9.8%)</t>
+    <t>(9.7%)</t>
   </si>
   <si>
     <t>3.5%</t>
@@ -968,7 +968,7 @@
     <t>19.1</t>
   </si>
   <si>
-    <t>69.7%</t>
+    <t>69.8%</t>
   </si>
   <si>
     <t>-R$ 31.922,75</t>
@@ -5710,10 +5710,10 @@
         <v>-0.13043478260869568</v>
       </c>
       <c r="T34" s="6">
-        <v>0.25893641453874677</v>
+        <v>0.32403861479009954</v>
       </c>
       <c r="U34" s="6">
-        <v>-0.061431260761531006</v>
+        <v>0.0036709394898217797</v>
       </c>
       <c r="V34" s="6">
         <v>0.096994805724154698</v>
@@ -8710,7 +8710,7 @@
         <v>19618</v>
       </c>
       <c r="B58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C58" s="4">
         <v>44</v>
@@ -8746,25 +8746,61 @@
       <c t="s" r="N58" s="4">
         <v>52</v>
       </c>
-      <c r="O58" s="5"/>
-      <c r="P58" s="5"/>
-      <c r="Q58" s="6"/>
-      <c r="R58" s="7"/>
-      <c r="S58" s="6"/>
-      <c r="T58" s="6"/>
-      <c r="U58" s="6"/>
-      <c r="V58" s="6"/>
-      <c r="W58" s="6"/>
-      <c r="X58" s="8"/>
-      <c r="Y58" s="6"/>
-      <c r="Z58" s="6"/>
-      <c r="AA58" s="8"/>
-      <c r="AB58" s="8"/>
-      <c r="AC58" s="8"/>
-      <c r="AD58" s="8"/>
-      <c r="AE58" s="6"/>
+      <c r="O58" s="5">
+        <v>6814.8500000000004</v>
+      </c>
+      <c r="P58" s="5">
+        <v>6814.8500000000004</v>
+      </c>
+      <c r="Q58" s="6">
+        <v>0.21624250428326675</v>
+      </c>
+      <c r="R58" s="7">
+        <v>77</v>
+      </c>
+      <c r="S58" s="6">
+        <v>0.13235294117647056</v>
+      </c>
+      <c r="T58" s="6">
+        <v>0.33288778182938727</v>
+      </c>
+      <c r="U58" s="6">
+        <v>-0.066537003749165421</v>
+      </c>
+      <c r="V58" s="6">
+        <v>0.01656705576791859</v>
+      </c>
+      <c r="W58" s="6">
+        <v>0.0024185418607893055</v>
+      </c>
+      <c r="X58" s="8">
+        <v>22.864779245283017</v>
+      </c>
+      <c r="Y58" s="6">
+        <v>0.69811320754716977</v>
+      </c>
+      <c r="Z58" s="6">
+        <v>0.018867924528301886</v>
+      </c>
+      <c r="AA58" s="8">
+        <v>3.4972217948717947</v>
+      </c>
+      <c r="AB58" s="8">
+        <v>5.2808169811320758</v>
+      </c>
+      <c r="AC58" s="8">
+        <v>8.9126069999999995</v>
+      </c>
+      <c r="AD58" s="8">
+        <v>15.774843396226414</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>0.84905660377358494</v>
+      </c>
       <c r="AF58" s="9"/>
-      <c r="AG58" s="5"/>
+      <c r="AG58" s="5">
+        <v>0</v>
+      </c>
       <c r="AH58" s="10">
         <v>2</v>
       </c>
@@ -24021,7 +24057,9 @@
       <c r="AB179" s="8">
         <v>2.0277791666666665</v>
       </c>
-      <c r="AC179" s="8"/>
+      <c r="AC179" s="8">
+        <v>5.7854150000000004</v>
+      </c>
       <c r="AD179" s="8">
         <v>12.738195833333334</v>
       </c>
